--- a/tracks.xlsx
+++ b/tracks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Work\Work\Tech Trek\Reciept System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981653C6-FC97-48CA-9C17-57487E7D1352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4010FBF-5418-4180-8ABB-D8D188CB0782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracks" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="37">
   <si>
     <t>University</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Alexandria University</t>
   </si>
   <si>
-    <t>Embedded Systems</t>
-  </si>
-  <si>
     <t>Cyber Security (SOC)</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>Devops</t>
   </si>
   <si>
-    <t>Internet of things</t>
-  </si>
-  <si>
     <t>Alexandria National University</t>
   </si>
   <si>
@@ -100,6 +94,48 @@
   </si>
   <si>
     <t>Backend Development (.Net)</t>
+  </si>
+  <si>
+    <t>Advanced Data Science (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Data Analysis &amp; Business Intelligence (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence(Ai) (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Frontend Development (Angular) (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Frontend Development (React) (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Backend Development (Node js) (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Backend Development (.Net) (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Flutter Development Diploma (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Computer Vision (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Automation (n8n) (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Cyber Security (SOC) (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Bug Bounty &amp; Ethical Hacking (+60 hr.)</t>
+  </si>
+  <si>
+    <t>Penetration Testing (+60 hr.)</t>
+  </si>
+  <si>
+    <t>AIET</t>
   </si>
 </sst>
 </file>
@@ -499,10 +535,10 @@
     </row>
     <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2">
         <v>140</v>
@@ -513,10 +549,10 @@
     </row>
     <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2">
         <v>120</v>
@@ -527,10 +563,10 @@
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2">
         <v>140</v>
@@ -541,10 +577,10 @@
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>140</v>
@@ -555,10 +591,10 @@
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2">
         <v>130</v>
@@ -569,10 +605,10 @@
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2">
         <v>120</v>
@@ -583,10 +619,10 @@
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2">
         <v>120</v>
@@ -597,10 +633,10 @@
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2">
         <v>140</v>
@@ -611,10 +647,10 @@
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2">
         <v>140</v>
@@ -625,10 +661,10 @@
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2">
         <v>140</v>
@@ -639,198 +675,198 @@
     </row>
     <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D12" s="2">
-        <v>3200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2">
-        <v>120</v>
-      </c>
-      <c r="D13" s="2">
-        <v>3200</v>
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>64</v>
+      </c>
+      <c r="D13">
+        <v>2500</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2">
-        <v>130</v>
-      </c>
-      <c r="D14" s="2">
-        <v>3200</v>
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>64</v>
+      </c>
+      <c r="D14">
+        <v>2500</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2">
-        <v>130</v>
-      </c>
-      <c r="D15" s="2">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>64</v>
+      </c>
+      <c r="D15">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2">
-        <v>140</v>
-      </c>
-      <c r="D16" s="2">
-        <v>4000</v>
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <v>60</v>
+      </c>
+      <c r="D16">
+        <v>2000</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2">
-        <v>64</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1000</v>
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>60</v>
+      </c>
+      <c r="D17">
+        <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="2">
-        <v>64</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1000</v>
+        <v>28</v>
+      </c>
+      <c r="C18">
+        <v>64</v>
+      </c>
+      <c r="D18">
+        <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2">
-        <v>64</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1000</v>
+        <v>29</v>
+      </c>
+      <c r="C19">
+        <v>64</v>
+      </c>
+      <c r="D19">
+        <v>2000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="2">
-        <v>60</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1000</v>
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>64</v>
+      </c>
+      <c r="D20">
+        <v>2500</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2">
+        <v>31</v>
+      </c>
+      <c r="C21">
         <v>60</v>
       </c>
-      <c r="D21" s="2">
-        <v>1000</v>
+      <c r="D21">
+        <v>2000</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2">
-        <v>64</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1000</v>
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>64</v>
+      </c>
+      <c r="D22">
+        <v>2500</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="2">
-        <v>64</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1000</v>
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>64</v>
+      </c>
+      <c r="D23">
+        <v>2500</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2">
-        <v>64</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1000</v>
+        <v>34</v>
+      </c>
+      <c r="C24">
+        <v>64</v>
+      </c>
+      <c r="D24">
+        <v>2500</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2">
-        <v>60</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1000</v>
+        <v>35</v>
+      </c>
+      <c r="C25">
+        <v>64</v>
+      </c>
+      <c r="D25">
+        <v>2500</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -838,7 +874,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C26" s="2">
         <v>64</v>
@@ -852,7 +888,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C27" s="2">
         <v>64</v>
@@ -866,7 +902,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C28" s="2">
         <v>64</v>
@@ -880,10 +916,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C29" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D29" s="2">
         <v>1000</v>
@@ -894,10 +930,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C30" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2">
         <v>1000</v>
@@ -908,22 +944,168 @@
         <v>4</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="2">
+        <v>64</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="2">
+        <v>64</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="2">
-        <v>64</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="4"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" s="3"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C33" s="2">
+        <v>64</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="2">
+        <v>60</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="2">
+        <v>64</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2">
+        <v>64</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="2">
+        <v>64</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="2">
+        <v>64</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2">
+        <v>64</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2">
+        <v>64</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B45" s="3"/>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">

--- a/tracks.xlsx
+++ b/tracks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Work\Work\Tech Trek\Reciept System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4010FBF-5418-4180-8ABB-D8D188CB0782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495B56AA-A7CA-45C8-9078-2D03AFFE13AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
   <si>
     <t>University</t>
   </si>
@@ -136,6 +136,69 @@
   </si>
   <si>
     <t>AIET</t>
+  </si>
+  <si>
+    <t>Advanced Data Science (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Data Analysis &amp; Business Intelligence (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence(Ai) (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Frontend Development (Angular) (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Frontend Development (React) (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Backend Development (Node js) (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Backend Development (.Net) (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Flutter Development Diploma (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Automation (n8n) (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Computer Vision (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Bug Bounty &amp; Ethical Hacking (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Cyber Security (SOC) (60 Hrs. – 12 Days)</t>
+  </si>
+  <si>
+    <t>Advanced Data Science (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Data Analysis &amp; Business Intelligence (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence(Ai) (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Flutter Development Diploma (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Full Stack (React &amp; Node Js) (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Automation (n8n) (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Computer Vision (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Bug Bounty &amp; Ethical Hacking (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Cyber Security (SOC) (120 Hrs. – 24 Days)</t>
   </si>
 </sst>
 </file>
@@ -514,7 +577,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" customWidth="1"/>
-    <col min="2" max="2" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.88671875" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
   </cols>
@@ -1083,39 +1146,295 @@
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="2">
+        <v>60</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2500</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="A42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="2">
+        <v>60</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2500</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="2">
+        <v>60</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2500</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="3"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B50" s="3"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B56" s="3"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B61" s="3"/>
+      <c r="A44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="2">
+        <v>60</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="2">
+        <v>60</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="2">
+        <v>60</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="2">
+        <v>60</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="2">
+        <v>60</v>
+      </c>
+      <c r="D48">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="2">
+        <v>60</v>
+      </c>
+      <c r="D49">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="2">
+        <v>60</v>
+      </c>
+      <c r="D50">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="2">
+        <v>60</v>
+      </c>
+      <c r="D51">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="2">
+        <v>60</v>
+      </c>
+      <c r="D52">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="2">
+        <v>120</v>
+      </c>
+      <c r="D53">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="2">
+        <v>120</v>
+      </c>
+      <c r="D54">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="2">
+        <v>120</v>
+      </c>
+      <c r="D55">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="2">
+        <v>120</v>
+      </c>
+      <c r="D56">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="2">
+        <v>120</v>
+      </c>
+      <c r="D57">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58" s="2">
+        <v>120</v>
+      </c>
+      <c r="D58">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="2">
+        <v>120</v>
+      </c>
+      <c r="D59">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="2">
+        <v>120</v>
+      </c>
+      <c r="D60">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C61" s="2">
+        <v>120</v>
+      </c>
+      <c r="D61">
+        <v>5000</v>
+      </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="3"/>

--- a/tracks.xlsx
+++ b/tracks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Work\Work\Tech Trek\Reciept System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495B56AA-A7CA-45C8-9078-2D03AFFE13AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD411E4-F9BE-498D-81DD-3174FC2DD968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="59">
   <si>
     <t>University</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Cyber Security (SOC) (120 Hrs. – 24 Days)</t>
+  </si>
+  <si>
+    <t>Benha National University</t>
   </si>
 </sst>
 </file>
@@ -248,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -256,7 +259,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -573,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" customWidth="1"/>
@@ -600,7 +602,7 @@
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="2">
@@ -614,7 +616,7 @@
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2">
@@ -628,7 +630,7 @@
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="2">
@@ -642,7 +644,7 @@
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="2">
@@ -656,7 +658,7 @@
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2">
@@ -670,7 +672,7 @@
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="2">
@@ -684,7 +686,7 @@
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2">
@@ -698,7 +700,7 @@
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
@@ -712,7 +714,7 @@
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2">
@@ -726,7 +728,7 @@
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2">
@@ -740,7 +742,7 @@
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2">
@@ -754,7 +756,7 @@
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C13">
@@ -768,7 +770,7 @@
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14">
@@ -782,7 +784,7 @@
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C15">
@@ -796,7 +798,7 @@
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C16">
@@ -810,7 +812,7 @@
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C17">
@@ -824,7 +826,7 @@
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C18">
@@ -838,7 +840,7 @@
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C19">
@@ -852,7 +854,7 @@
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C20">
@@ -866,7 +868,7 @@
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C21">
@@ -880,7 +882,7 @@
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C22">
@@ -894,7 +896,7 @@
       <c r="A23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C23">
@@ -908,7 +910,7 @@
       <c r="A24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C24">
@@ -922,7 +924,7 @@
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C25">
@@ -936,7 +938,7 @@
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="2">
@@ -950,7 +952,7 @@
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2">
@@ -964,7 +966,7 @@
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C28" s="2">
@@ -978,7 +980,7 @@
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2">
@@ -992,7 +994,7 @@
       <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C30" s="2">
@@ -1006,7 +1008,7 @@
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="2">
@@ -1020,7 +1022,7 @@
       <c r="A32" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="2">
@@ -1034,7 +1036,7 @@
       <c r="A33" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="2">
@@ -1048,7 +1050,7 @@
       <c r="A34" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="2">
@@ -1062,7 +1064,7 @@
       <c r="A35" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2">
@@ -1076,7 +1078,7 @@
       <c r="A36" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="2">
@@ -1090,7 +1092,7 @@
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C37" s="2">
@@ -1104,7 +1106,7 @@
       <c r="A38" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2">
@@ -1118,7 +1120,7 @@
       <c r="A39" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="2">
@@ -1132,7 +1134,7 @@
       <c r="A40" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2">
@@ -1146,7 +1148,7 @@
       <c r="A41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C41" s="2">
@@ -1160,7 +1162,7 @@
       <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="2">
@@ -1174,7 +1176,7 @@
       <c r="A43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C43" s="2">
@@ -1188,7 +1190,7 @@
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C44" s="2">
@@ -1202,7 +1204,7 @@
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C45" s="2">
@@ -1216,7 +1218,7 @@
       <c r="A46" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="2">
@@ -1230,7 +1232,7 @@
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="2">
@@ -1244,7 +1246,7 @@
       <c r="A48" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C48" s="2">
@@ -1258,7 +1260,7 @@
       <c r="A49" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C49" s="2">
@@ -1272,7 +1274,7 @@
       <c r="A50" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C50" s="2">
@@ -1286,7 +1288,7 @@
       <c r="A51" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C51" s="2">
@@ -1300,7 +1302,7 @@
       <c r="A52" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C52" s="2">
@@ -1314,7 +1316,7 @@
       <c r="A53" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C53" s="2">
@@ -1328,7 +1330,7 @@
       <c r="A54" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C54" s="2">
@@ -1342,7 +1344,7 @@
       <c r="A55" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C55" s="2">
@@ -1356,7 +1358,7 @@
       <c r="A56" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C56" s="2">
@@ -1370,7 +1372,7 @@
       <c r="A57" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C57" s="2">
@@ -1384,7 +1386,7 @@
       <c r="A58" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C58" s="2">
@@ -1398,7 +1400,7 @@
       <c r="A59" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C59" s="2">
@@ -1412,7 +1414,7 @@
       <c r="A60" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C60" s="2">
@@ -1426,7 +1428,7 @@
       <c r="A61" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C61" s="2">
@@ -1436,17 +1438,341 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B66" s="3"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B71" s="3"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B76" s="3"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B81" s="3"/>
+    <row r="62" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="2">
+        <v>64</v>
+      </c>
+      <c r="D62">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>58</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="2">
+        <v>64</v>
+      </c>
+      <c r="D63">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" s="2">
+        <v>64</v>
+      </c>
+      <c r="D64">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="2">
+        <v>60</v>
+      </c>
+      <c r="D65">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>58</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="2">
+        <v>60</v>
+      </c>
+      <c r="D66">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="2">
+        <v>64</v>
+      </c>
+      <c r="D67">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="2">
+        <v>64</v>
+      </c>
+      <c r="D68">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="2">
+        <v>64</v>
+      </c>
+      <c r="D69">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="2">
+        <v>60</v>
+      </c>
+      <c r="D70">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="2">
+        <v>64</v>
+      </c>
+      <c r="D71">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="2">
+        <v>64</v>
+      </c>
+      <c r="D72">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>58</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="2">
+        <v>64</v>
+      </c>
+      <c r="D73">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>58</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74" s="2">
+        <v>64</v>
+      </c>
+      <c r="D74">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>58</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75">
+        <v>120</v>
+      </c>
+      <c r="D75">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>58</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76">
+        <v>120</v>
+      </c>
+      <c r="D76">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>58</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77">
+        <v>120</v>
+      </c>
+      <c r="D77">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78">
+        <v>120</v>
+      </c>
+      <c r="D78">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>58</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79">
+        <v>120</v>
+      </c>
+      <c r="D79">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>58</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80">
+        <v>120</v>
+      </c>
+      <c r="D80">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>58</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81">
+        <v>120</v>
+      </c>
+      <c r="D81">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>58</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82">
+        <v>120</v>
+      </c>
+      <c r="D82">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83">
+        <v>120</v>
+      </c>
+      <c r="D83">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>58</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>120</v>
+      </c>
+      <c r="D84">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85">
+        <v>120</v>
+      </c>
+      <c r="D85">
+        <v>3500</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tracks.xlsx
+++ b/tracks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Work\Work\Tech Trek\Reciept System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD411E4-F9BE-498D-81DD-3174FC2DD968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F499372-EB17-4109-995A-1BB46C2C7A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="60">
   <si>
     <t>University</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>Benha National University</t>
+  </si>
+  <si>
+    <t>Intensive Diploma</t>
   </si>
 </sst>
 </file>
@@ -575,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" customWidth="1"/>
@@ -1774,6 +1777,160 @@
         <v>3500</v>
       </c>
     </row>
+    <row r="86" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="2">
+        <v>140</v>
+      </c>
+      <c r="D86" s="2">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" s="2">
+        <v>120</v>
+      </c>
+      <c r="D87" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="2">
+        <v>140</v>
+      </c>
+      <c r="D88" s="2">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="2">
+        <v>140</v>
+      </c>
+      <c r="D89" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="2">
+        <v>130</v>
+      </c>
+      <c r="D90" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" s="2">
+        <v>120</v>
+      </c>
+      <c r="D91" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="2">
+        <v>120</v>
+      </c>
+      <c r="D92" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="2">
+        <v>140</v>
+      </c>
+      <c r="D93" s="2">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="2">
+        <v>140</v>
+      </c>
+      <c r="D94" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="2">
+        <v>140</v>
+      </c>
+      <c r="D95" s="2">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2">
+        <v>140</v>
+      </c>
+      <c r="D96" s="2">
+        <v>4000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
